--- a/과목 데이터.xlsx
+++ b/과목 데이터.xlsx
@@ -15,480 +15,338 @@
 </x:workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author>데이터 확인</x:author>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="M4:M4" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 소프트웨어학과. 현재 학과 목록에서 코드 2의 학과: 소프트웨어학. 적용 전 확인하세요.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M5:M5" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 정보보안학과. 현재 학과 목록에서 코드 3의 학과: 경영학과. 적용 전 확인하세요.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M6:M6" authorId="0">
-      <x:text/>
-    </x:comment>
-    <x:comment ref="M7:M7" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 토목공학과. 현재 학과 목록에서 코드 5의 학과: 특수전공. 적용 전 확인하세요.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M8:M8" authorId="0">
-      <x:text/>
-    </x:comment>
-    <x:comment ref="M9:M9" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 법학과. 코드 7는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M12:M12" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 교양학부. 코드 10는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M13:M13" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 교양학부. 코드 10는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M14:M14" authorId="0">
-      <x:text/>
-    </x:comment>
-    <x:comment ref="M15:M15" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 교양학부. 코드 10는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M16:M16" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 교양학부. 코드 10는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M17:M17" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 인공지능학과. 코드 11는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-    <x:comment ref="M18:M18" authorId="0">
-      <x:text/>
-    </x:comment>
-    <x:comment ref="M19:M19" authorId="0">
-      <x:text>
-        <x:r>
-          <x:rPr>
-            <x:rFont val="굴림"/>
-            <x:sz val="9"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-          <x:t>원본 과목의 학과: 데이터사이언스학과. 코드 12는 현재 학과 목록에 없습니다. 적용 전 학과 등록 또는 코드 확인이 필요합니다.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="108">
   <x:si>
+    <x:t>균형기초학문영역(균형학문영역)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취·창업실무영역(비전설계영역)</x:t>
+  </x:si>
+  <x:si>
     <x:t>구분</x:t>
   </x:si>
   <x:si>
+    <x:t>월</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과목명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강의실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박교수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>김교수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요일</x:t>
+  </x:si>
+  <x:si>
     <x:t>전공</x:t>
   </x:si>
   <x:si>
-    <x:t>과목명</x:t>
+    <x:t>화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영역</x:t>
   </x:si>
   <x:si>
     <x:t>분반</x:t>
   </x:si>
   <x:si>
-    <x:t>학점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강의실</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>영역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월</x:t>
-  </x:si>
-  <x:si>
     <x:t>3,4</x:t>
   </x:si>
   <x:si>
-    <x:t>박교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화</x:t>
+    <x:t>정교수</x:t>
   </x:si>
   <x:si>
     <x:t>이교수</x:t>
   </x:si>
   <x:si>
+    <x:t>온라인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교양</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최교수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이강사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
-    <x:t>목</x:t>
+    <x:t>금</x:t>
   </x:si>
   <x:si>
     <x:t>1,2</x:t>
   </x:si>
   <x:si>
-    <x:t>온라인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최교수</x:t>
+    <x:t>한교수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김법학</x:t>
   </x:si>
   <x:si>
     <x:t>박강사</x:t>
   </x:si>
   <x:si>
-    <x:t>이강사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김법학</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교양</x:t>
-  </x:si>
-  <x:si>
     <x:t>강교수</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
+    <x:t>IT Hall 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대학생활과 진로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IT Hall 202</x:t>
   </x:si>
   <x:si>
     <x:t>컴퓨터 네트워크</x:t>
   </x:si>
   <x:si>
-    <x:t>IT Hall 302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대학생활과 진로</x:t>
+    <x:t>IT Hall 301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IT Hall 205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현대사회와 문화</x:t>
   </x:si>
   <x:si>
     <x:t>온라인/오프라인</x:t>
   </x:si>
   <x:si>
-    <x:t>IT Hall 202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IT Hall 301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IT Hall 205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>균형기초학문영역(균형학문영역)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>취·창업실무영역(비전설계영역)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현대사회와 문화</x:t>
+    <x:t>디지털 리터러시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디지털 시대의 이해</x:t>
   </x:si>
   <x:si>
     <x:t>교양 필수 선택</x:t>
   </x:si>
   <x:si>
-    <x:t>디지털 리터러시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디지털 시대의 이해</x:t>
+    <x:t>ME201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공학관 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전공 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건축관 301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학수번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작교시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CS201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하위 영역 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자료구조</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오프라인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토목공학개론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전공 필수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하위 영역 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당교수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이수 구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대상학년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료교시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제외 학과코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SW201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학과코드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웹프로그래밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GE304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GE202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인공지능 기초</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인문관 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소프트웨어공학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대학 글쓰기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진로·취업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CS305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인문관 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데이터 분석</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기계공학개론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공학관 202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>민법총칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인간과 사회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이크로디그리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GE405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAW301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교양 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정보보안개론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>법학관 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인문과 철학</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI관 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CE301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GE101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>건축학개론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>글쓰기·표현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이크로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사회와 문화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI관 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의사소통 영역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CS401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GE303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교양 필수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인문관 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머신러닝 실습</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인문관 105</x:t>
   </x:si>
   <x:si>
     <x:t>경제와 사회(사회와 문화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자료구조</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전공 필수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학수번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대상학년</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작교시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료교시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하위 영역 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제외 학과코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CS201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학과코드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담당교수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이수 구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하위 영역 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SW201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오프라인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ME201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전공 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공학관 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건축관 301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토목공학개론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소프트웨어공학</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CE301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기계공학개론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CS305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정보보안개론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공학관 202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>건축학개론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LAW301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>민법총칙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>법학관 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GE405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교양 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인문과 철학</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마이크로디그리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI관 201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진로·취업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GE101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인간과 사회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>글쓰기·표현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마이크로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인문관 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웹프로그래밍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GE304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GE202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대학 글쓰기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인공지능 기초</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인문관 302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데이터 분석</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의사소통 영역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머신러닝 실습</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교양 필수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인문관 105</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI관 302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사회와 문화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CS401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인문관 201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GE303</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="ë§ì ê³ ë"/>
       <x:sz val="12"/>
@@ -522,11 +380,6 @@
     <x:font>
       <x:name val="돋움"/>
       <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="굴림"/>
-      <x:sz val="9"/>
       <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
@@ -1531,90 +1384,90 @@
   <x:sheetData>
     <x:row r="1" spans="1:19" ht="17.25" customHeight="1">
       <x:c r="A1" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K1" t="s">
+      <x:c r="L1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="N1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="P1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Q1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="R1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="O1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="P1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="Q1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="R1" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="S1" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
       <x:c r="A2" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G2" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G2" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I2" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="I2" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="J2">
         <x:v>3</x:v>
@@ -1629,10 +1482,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N2" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="P2">
         <x:v>2</x:v>
@@ -1641,39 +1494,39 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R2" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
       <x:c r="A3" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G3" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H3" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I3" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="I3" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="J3">
         <x:v>3</x:v>
@@ -1688,10 +1541,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N3" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O3" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P3">
         <x:v>2</x:v>
@@ -1700,39 +1553,39 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R3" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19">
       <x:c r="A4" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G4" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J4">
         <x:v>3</x:v>
@@ -1747,10 +1600,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N4" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O4" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="P4">
         <x:v>4</x:v>
@@ -1762,36 +1615,36 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="S4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:19">
       <x:c r="A5" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G5" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J5">
         <x:v>3</x:v>
@@ -1806,10 +1659,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N5" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O5" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="P5">
         <x:v>2</x:v>
@@ -1818,39 +1671,39 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R5" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="S5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:19">
       <x:c r="A6" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G6" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J6">
         <x:v>3</x:v>
@@ -1865,10 +1718,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N6" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O6" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="P6">
         <x:v>5</x:v>
@@ -1877,39 +1730,39 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="R6" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:19">
       <x:c r="A7" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G7" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J7">
         <x:v>3</x:v>
@@ -1924,10 +1777,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N7" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O7" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P7">
         <x:v>6</x:v>
@@ -1936,39 +1789,39 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="R7" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:19">
       <x:c r="A8" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G8" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J8">
         <x:v>3</x:v>
@@ -1983,10 +1836,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="N8" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O8" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="P8">
         <x:v>1</x:v>
@@ -1995,39 +1848,39 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R8" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:19">
       <x:c r="A9" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G9" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J9">
         <x:v>3</x:v>
@@ -2042,10 +1895,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="N9" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O9" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P9">
         <x:v>2</x:v>
@@ -2054,39 +1907,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="R9" t="s">
-        <x:v>77</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="S9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:19">
       <x:c r="A10" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G10" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10">
         <x:v>3</x:v>
@@ -2101,10 +1954,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N10" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O10" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="P10">
         <x:v>4</x:v>
@@ -2116,36 +1969,36 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="S10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:19">
       <x:c r="A11" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G11" t="s">
-        <x:v>90</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J11">
         <x:v>3</x:v>
@@ -2160,10 +2013,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N11" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O11" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P11">
         <x:v>4</x:v>
@@ -2172,39 +2025,39 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="R11" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="S11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:19">
       <x:c r="A12" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>40</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G12" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J12">
         <x:v>2</x:v>
@@ -2219,10 +2072,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O12" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P12">
         <x:v>4</x:v>
@@ -2231,39 +2084,39 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="R12" t="s">
-        <x:v>89</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:19">
       <x:c r="A13" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>79</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>45</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G13" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J13">
         <x:v>3</x:v>
@@ -2278,10 +2131,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N13" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O13" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="P13">
         <x:v>5</x:v>
@@ -2290,39 +2143,39 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="R13" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="S13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:19">
       <x:c r="A14" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>79</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>39</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G14" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J14">
         <x:v>3</x:v>
@@ -2337,10 +2190,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N14" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O14" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P14">
         <x:v>3</x:v>
@@ -2349,39 +2202,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="R14" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="S14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:19">
       <x:c r="A15" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>39</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E15" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E15" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G15" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H15" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I15" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="I15" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="J15">
         <x:v>3</x:v>
@@ -2399,48 +2252,48 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="O15" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P15" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Q15" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="R15" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="S15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:19">
       <x:c r="A16" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D16" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E16" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="G16" t="s">
-        <x:v>93</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J16">
         <x:v>2</x:v>
@@ -2455,10 +2308,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N16" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O16" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P16">
         <x:v>1</x:v>
@@ -2467,39 +2320,39 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R16" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="S16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:19">
       <x:c r="A17" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G17" t="s">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J17">
         <x:v>3</x:v>
@@ -2514,10 +2367,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N17" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O17" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="P17">
         <x:v>6</x:v>
@@ -2526,39 +2379,39 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="R17" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="S17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:19">
       <x:c r="A18" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G18" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J18">
         <x:v>3</x:v>
@@ -2573,10 +2426,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N18" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O18" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P18">
         <x:v>6</x:v>
@@ -2585,39 +2438,39 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="R18" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="S18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:19">
       <x:c r="A19" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G19" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J19">
         <x:v>3</x:v>
@@ -2635,25 +2488,24 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="O19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="P19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="Q19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="R19" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="S19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:S19"/>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <x:legacyDrawing r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/과목 데이터.xlsx
+++ b/과목 데이터.xlsx
@@ -489,16 +489,16 @@
       <c r="I2" t="str">
         <v>김교수</v>
       </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>40</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
+      <c r="J2" t="str">
+        <v>3</v>
+      </c>
+      <c r="K2" t="str">
+        <v>3997</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2</v>
+      </c>
+      <c r="M2" t="str">
         <v>1</v>
       </c>
       <c r="N2" t="str">
@@ -507,10 +507,10 @@
       <c r="O2" t="str">
         <v>월</v>
       </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="Q2">
+      <c r="P2" t="str">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="str">
         <v>3</v>
       </c>
       <c r="R2" t="str">
@@ -548,16 +548,16 @@
       <c r="I3" t="str">
         <v>김교수</v>
       </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
+      <c r="J3" t="str">
+        <v>3</v>
+      </c>
+      <c r="K3" t="str">
+        <v>3997</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2</v>
+      </c>
+      <c r="M3" t="str">
         <v>1</v>
       </c>
       <c r="N3" t="str">
@@ -566,10 +566,10 @@
       <c r="O3" t="str">
         <v>수</v>
       </c>
-      <c r="P3">
-        <v>2</v>
-      </c>
-      <c r="Q3">
+      <c r="P3" t="str">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="str">
         <v>3</v>
       </c>
       <c r="R3" t="str">
@@ -589,6 +589,9 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
       <c r="E4" t="str">
         <v/>
       </c>
@@ -608,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -663,16 +666,16 @@
       <c r="I5" t="str">
         <v>이교수</v>
       </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
+      <c r="J5" t="str">
+        <v>3</v>
+      </c>
+      <c r="K5" t="str">
         <v>40</v>
       </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
+      <c r="L5" t="str">
+        <v>3</v>
+      </c>
+      <c r="M5" t="str">
         <v>13</v>
       </c>
       <c r="N5" t="str">
@@ -681,10 +684,10 @@
       <c r="O5" t="str">
         <v>목</v>
       </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5">
+      <c r="P5" t="str">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="str">
         <v>3</v>
       </c>
       <c r="R5" t="str">
@@ -722,16 +725,16 @@
       <c r="I6" t="str">
         <v>최교수</v>
       </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
+      <c r="J6" t="str">
+        <v>3</v>
+      </c>
+      <c r="K6" t="str">
         <v>40</v>
       </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
+      <c r="L6" t="str">
+        <v>2</v>
+      </c>
+      <c r="M6" t="str">
         <v>14</v>
       </c>
       <c r="N6" t="str">
@@ -740,10 +743,10 @@
       <c r="O6" t="str">
         <v>월</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="str">
         <v>5</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="str">
         <v>6</v>
       </c>
       <c r="R6" t="str">
@@ -760,6 +763,12 @@
       <c r="B7" t="str">
         <v>전공 선택</v>
       </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
       <c r="E7" t="str">
         <v/>
       </c>
@@ -775,16 +784,16 @@
       <c r="I7" t="str">
         <v>정교수</v>
       </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
+      <c r="J7" t="str">
+        <v>3</v>
+      </c>
+      <c r="K7" t="str">
         <v>40</v>
       </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
+      <c r="L7" t="str">
+        <v>3</v>
+      </c>
+      <c r="M7" t="str">
         <v>15</v>
       </c>
       <c r="N7" t="str">
@@ -793,10 +802,10 @@
       <c r="O7" t="str">
         <v>수</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="str">
         <v>6</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="str">
         <v>7</v>
       </c>
       <c r="R7" t="str">
@@ -834,16 +843,16 @@
       <c r="I8" t="str">
         <v>한교수</v>
       </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
-      <c r="K8">
+      <c r="J8" t="str">
+        <v>3</v>
+      </c>
+      <c r="K8" t="str">
         <v>35</v>
       </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-      <c r="M8">
+      <c r="L8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M8" t="str">
         <v>6</v>
       </c>
       <c r="N8" t="str">
@@ -852,10 +861,10 @@
       <c r="O8" t="str">
         <v>화</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="str">
         <v>1</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="str">
         <v>2</v>
       </c>
       <c r="R8" t="str">
@@ -875,6 +884,9 @@
       <c r="C9" t="str">
         <v/>
       </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
       <c r="E9" t="str">
         <v/>
       </c>
@@ -890,16 +902,16 @@
       <c r="I9" t="str">
         <v>김법학</v>
       </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9">
+      <c r="J9" t="str">
+        <v>3</v>
+      </c>
+      <c r="K9" t="str">
         <v>50</v>
       </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-      <c r="M9">
+      <c r="L9" t="str">
+        <v>3</v>
+      </c>
+      <c r="M9" t="str">
         <v>7</v>
       </c>
       <c r="N9" t="str">
@@ -908,10 +920,10 @@
       <c r="O9" t="str">
         <v>금</v>
       </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="Q9">
+      <c r="P9" t="str">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="str">
         <v>4</v>
       </c>
       <c r="R9" t="str">
@@ -949,16 +961,16 @@
       <c r="I10" t="str">
         <v>박교수</v>
       </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10">
+      <c r="J10" t="str">
+        <v>3</v>
+      </c>
+      <c r="K10" t="str">
         <v>40</v>
       </c>
-      <c r="L10">
-        <v>3</v>
-      </c>
-      <c r="M10">
+      <c r="L10" t="str">
+        <v>3</v>
+      </c>
+      <c r="M10" t="str">
         <v>1</v>
       </c>
       <c r="N10" t="str">
@@ -967,10 +979,10 @@
       <c r="O10" t="str">
         <v>화</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="str">
         <v>4</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="str">
         <v>5</v>
       </c>
       <c r="R10" t="str">
@@ -1008,16 +1020,16 @@
       <c r="I11" t="str">
         <v>박교수</v>
       </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11">
+      <c r="J11" t="str">
+        <v>3</v>
+      </c>
+      <c r="K11" t="str">
         <v>40</v>
       </c>
-      <c r="L11">
-        <v>3</v>
-      </c>
-      <c r="M11">
+      <c r="L11" t="str">
+        <v>3</v>
+      </c>
+      <c r="M11" t="str">
         <v>1</v>
       </c>
       <c r="N11" t="str">
@@ -1026,10 +1038,10 @@
       <c r="O11" t="str">
         <v>금</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="str">
         <v>4</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="str">
         <v>5</v>
       </c>
       <c r="R11" t="str">
@@ -1067,16 +1079,16 @@
       <c r="I12" t="str">
         <v>이강사</v>
       </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12">
+      <c r="J12" t="str">
+        <v>2</v>
+      </c>
+      <c r="K12" t="str">
         <v>50</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="str">
         <v>1</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="str">
         <v>10</v>
       </c>
       <c r="N12" t="str">
@@ -1085,10 +1097,10 @@
       <c r="O12" t="str">
         <v>수</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="str">
         <v>4</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="str">
         <v>5</v>
       </c>
       <c r="R12" t="str">
@@ -1126,16 +1138,16 @@
       <c r="I13" t="str">
         <v>최교수</v>
       </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13">
+      <c r="J13" t="str">
+        <v>3</v>
+      </c>
+      <c r="K13" t="str">
         <v>45</v>
       </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
+      <c r="L13" t="str">
+        <v>2</v>
+      </c>
+      <c r="M13" t="str">
         <v>10</v>
       </c>
       <c r="N13" t="str">
@@ -1144,10 +1156,10 @@
       <c r="O13" t="str">
         <v>목</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="str">
         <v>5</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="str">
         <v>6</v>
       </c>
       <c r="R13" t="str">
@@ -1185,16 +1197,16 @@
       <c r="I14" t="str">
         <v>정교수</v>
       </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14">
+      <c r="J14" t="str">
+        <v>3</v>
+      </c>
+      <c r="K14" t="str">
         <v>40</v>
       </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-      <c r="M14">
+      <c r="L14" t="str">
+        <v>2</v>
+      </c>
+      <c r="M14" t="str">
         <v>10</v>
       </c>
       <c r="N14" t="str">
@@ -1203,10 +1215,10 @@
       <c r="O14" t="str">
         <v>수</v>
       </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-      <c r="Q14">
+      <c r="P14" t="str">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="str">
         <v>4</v>
       </c>
       <c r="R14" t="str">
@@ -1244,16 +1256,16 @@
       <c r="I15" t="str">
         <v>김교수</v>
       </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
+      <c r="J15" t="str">
+        <v>3</v>
+      </c>
+      <c r="K15" t="str">
         <v>50</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="str">
         <v>1</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="str">
         <v>10</v>
       </c>
       <c r="N15" t="str">
@@ -1303,16 +1315,16 @@
       <c r="I16" t="str">
         <v>박강사</v>
       </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16">
+      <c r="J16" t="str">
+        <v>2</v>
+      </c>
+      <c r="K16" t="str">
         <v>45</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="str">
         <v>1</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="str">
         <v>10</v>
       </c>
       <c r="N16" t="str">
@@ -1321,10 +1333,10 @@
       <c r="O16" t="str">
         <v>금</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="str">
         <v>1</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="str">
         <v>2</v>
       </c>
       <c r="R16" t="str">
@@ -1362,16 +1374,16 @@
       <c r="I17" t="str">
         <v>강교수</v>
       </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17">
+      <c r="J17" t="str">
+        <v>3</v>
+      </c>
+      <c r="K17" t="str">
         <v>30</v>
       </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17">
+      <c r="L17" t="str">
+        <v>2</v>
+      </c>
+      <c r="M17" t="str">
         <v>11</v>
       </c>
       <c r="N17" t="str">
@@ -1380,10 +1392,10 @@
       <c r="O17" t="str">
         <v>월</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="str">
         <v>6</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="str">
         <v>7</v>
       </c>
       <c r="R17" t="str">
@@ -1421,16 +1433,16 @@
       <c r="I18" t="str">
         <v>이교수</v>
       </c>
-      <c r="J18">
-        <v>3</v>
-      </c>
-      <c r="K18">
+      <c r="J18" t="str">
+        <v>3</v>
+      </c>
+      <c r="K18" t="str">
         <v>30</v>
       </c>
-      <c r="L18">
-        <v>3</v>
-      </c>
-      <c r="M18">
+      <c r="L18" t="str">
+        <v>3</v>
+      </c>
+      <c r="M18" t="str">
         <v>11</v>
       </c>
       <c r="N18" t="str">
@@ -1439,10 +1451,10 @@
       <c r="O18" t="str">
         <v>수</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="str">
         <v>6</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="str">
         <v>8</v>
       </c>
       <c r="R18" t="str">
@@ -1480,16 +1492,16 @@
       <c r="I19" t="str">
         <v>박교수</v>
       </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
-      <c r="K19">
+      <c r="J19" t="str">
+        <v>3</v>
+      </c>
+      <c r="K19" t="str">
         <v>35</v>
       </c>
-      <c r="L19">
-        <v>3</v>
-      </c>
-      <c r="M19">
+      <c r="L19" t="str">
+        <v>3</v>
+      </c>
+      <c r="M19" t="str">
         <v>12</v>
       </c>
       <c r="N19" t="str">
@@ -1539,16 +1551,16 @@
       <c r="I20" t="str">
         <v>이교수</v>
       </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-      <c r="K20">
+      <c r="J20" t="str">
+        <v>2</v>
+      </c>
+      <c r="K20" t="str">
         <v>40</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="str">
         <v>1</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="str">
         <v>1</v>
       </c>
       <c r="N20" t="str">
@@ -1557,10 +1569,10 @@
       <c r="O20" t="str">
         <v>월</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="str">
         <v>1</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="str">
         <v>1</v>
       </c>
       <c r="R20" t="str">
@@ -1571,8 +1583,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S19"/>
-  <pageMargins left="0.6997222304344177" right="0.6997222304344177" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:S20"/>
   </ignoredErrors>

--- a/과목 데이터.xlsx
+++ b/과목 데이터.xlsx
@@ -489,16 +489,16 @@
       <c r="I2" t="str">
         <v>김교수</v>
       </c>
-      <c r="J2" t="str">
-        <v>3</v>
-      </c>
-      <c r="K2" t="str">
-        <v>3997</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2</v>
-      </c>
-      <c r="M2" t="str">
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>40</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="str">
@@ -507,10 +507,10 @@
       <c r="O2" t="str">
         <v>월</v>
       </c>
-      <c r="P2" t="str">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="str">
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
         <v>3</v>
       </c>
       <c r="R2" t="str">
@@ -548,16 +548,16 @@
       <c r="I3" t="str">
         <v>김교수</v>
       </c>
-      <c r="J3" t="str">
-        <v>3</v>
-      </c>
-      <c r="K3" t="str">
-        <v>3997</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2</v>
-      </c>
-      <c r="M3" t="str">
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="str">
@@ -566,10 +566,10 @@
       <c r="O3" t="str">
         <v>수</v>
       </c>
-      <c r="P3" t="str">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="str">
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
         <v>3</v>
       </c>
       <c r="R3" t="str">
@@ -589,9 +589,6 @@
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
       <c r="E4" t="str">
         <v/>
       </c>
@@ -611,7 +608,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -666,16 +663,16 @@
       <c r="I5" t="str">
         <v>이교수</v>
       </c>
-      <c r="J5" t="str">
-        <v>3</v>
-      </c>
-      <c r="K5" t="str">
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>40</v>
       </c>
-      <c r="L5" t="str">
-        <v>3</v>
-      </c>
-      <c r="M5" t="str">
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
         <v>13</v>
       </c>
       <c r="N5" t="str">
@@ -684,10 +681,10 @@
       <c r="O5" t="str">
         <v>목</v>
       </c>
-      <c r="P5" t="str">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="str">
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
         <v>3</v>
       </c>
       <c r="R5" t="str">
@@ -725,16 +722,16 @@
       <c r="I6" t="str">
         <v>최교수</v>
       </c>
-      <c r="J6" t="str">
-        <v>3</v>
-      </c>
-      <c r="K6" t="str">
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>40</v>
       </c>
-      <c r="L6" t="str">
-        <v>2</v>
-      </c>
-      <c r="M6" t="str">
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
         <v>14</v>
       </c>
       <c r="N6" t="str">
@@ -743,10 +740,10 @@
       <c r="O6" t="str">
         <v>월</v>
       </c>
-      <c r="P6" t="str">
+      <c r="P6">
         <v>5</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="Q6">
         <v>6</v>
       </c>
       <c r="R6" t="str">
@@ -763,12 +760,6 @@
       <c r="B7" t="str">
         <v>전공 선택</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
       <c r="E7" t="str">
         <v/>
       </c>
@@ -784,16 +775,16 @@
       <c r="I7" t="str">
         <v>정교수</v>
       </c>
-      <c r="J7" t="str">
-        <v>3</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
         <v>40</v>
       </c>
-      <c r="L7" t="str">
-        <v>3</v>
-      </c>
-      <c r="M7" t="str">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
       <c r="N7" t="str">
@@ -802,10 +793,10 @@
       <c r="O7" t="str">
         <v>수</v>
       </c>
-      <c r="P7" t="str">
+      <c r="P7">
         <v>6</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="Q7">
         <v>7</v>
       </c>
       <c r="R7" t="str">
@@ -843,16 +834,16 @@
       <c r="I8" t="str">
         <v>한교수</v>
       </c>
-      <c r="J8" t="str">
-        <v>3</v>
-      </c>
-      <c r="K8" t="str">
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
         <v>35</v>
       </c>
-      <c r="L8" t="str">
-        <v>2</v>
-      </c>
-      <c r="M8" t="str">
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
         <v>6</v>
       </c>
       <c r="N8" t="str">
@@ -861,10 +852,10 @@
       <c r="O8" t="str">
         <v>화</v>
       </c>
-      <c r="P8" t="str">
+      <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8" t="str">
@@ -884,9 +875,6 @@
       <c r="C9" t="str">
         <v/>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
       <c r="E9" t="str">
         <v/>
       </c>
@@ -902,16 +890,16 @@
       <c r="I9" t="str">
         <v>김법학</v>
       </c>
-      <c r="J9" t="str">
-        <v>3</v>
-      </c>
-      <c r="K9" t="str">
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
         <v>50</v>
       </c>
-      <c r="L9" t="str">
-        <v>3</v>
-      </c>
-      <c r="M9" t="str">
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
         <v>7</v>
       </c>
       <c r="N9" t="str">
@@ -920,10 +908,10 @@
       <c r="O9" t="str">
         <v>금</v>
       </c>
-      <c r="P9" t="str">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="str">
+      <c r="P9">
+        <v>2</v>
+      </c>
+      <c r="Q9">
         <v>4</v>
       </c>
       <c r="R9" t="str">
@@ -961,16 +949,16 @@
       <c r="I10" t="str">
         <v>박교수</v>
       </c>
-      <c r="J10" t="str">
-        <v>3</v>
-      </c>
-      <c r="K10" t="str">
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
         <v>40</v>
       </c>
-      <c r="L10" t="str">
-        <v>3</v>
-      </c>
-      <c r="M10" t="str">
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="str">
@@ -979,10 +967,10 @@
       <c r="O10" t="str">
         <v>화</v>
       </c>
-      <c r="P10" t="str">
+      <c r="P10">
         <v>4</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10" t="str">
@@ -1020,16 +1008,16 @@
       <c r="I11" t="str">
         <v>박교수</v>
       </c>
-      <c r="J11" t="str">
-        <v>3</v>
-      </c>
-      <c r="K11" t="str">
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
         <v>40</v>
       </c>
-      <c r="L11" t="str">
-        <v>3</v>
-      </c>
-      <c r="M11" t="str">
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" t="str">
@@ -1038,10 +1026,10 @@
       <c r="O11" t="str">
         <v>금</v>
       </c>
-      <c r="P11" t="str">
+      <c r="P11">
         <v>4</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="Q11">
         <v>5</v>
       </c>
       <c r="R11" t="str">
@@ -1079,16 +1067,16 @@
       <c r="I12" t="str">
         <v>이강사</v>
       </c>
-      <c r="J12" t="str">
-        <v>2</v>
-      </c>
-      <c r="K12" t="str">
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
         <v>50</v>
       </c>
-      <c r="L12" t="str">
+      <c r="L12">
         <v>1</v>
       </c>
-      <c r="M12" t="str">
+      <c r="M12">
         <v>10</v>
       </c>
       <c r="N12" t="str">
@@ -1097,10 +1085,10 @@
       <c r="O12" t="str">
         <v>수</v>
       </c>
-      <c r="P12" t="str">
+      <c r="P12">
         <v>4</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="Q12">
         <v>5</v>
       </c>
       <c r="R12" t="str">
@@ -1138,16 +1126,16 @@
       <c r="I13" t="str">
         <v>최교수</v>
       </c>
-      <c r="J13" t="str">
-        <v>3</v>
-      </c>
-      <c r="K13" t="str">
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
         <v>45</v>
       </c>
-      <c r="L13" t="str">
-        <v>2</v>
-      </c>
-      <c r="M13" t="str">
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
         <v>10</v>
       </c>
       <c r="N13" t="str">
@@ -1156,10 +1144,10 @@
       <c r="O13" t="str">
         <v>목</v>
       </c>
-      <c r="P13" t="str">
+      <c r="P13">
         <v>5</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="Q13">
         <v>6</v>
       </c>
       <c r="R13" t="str">
@@ -1197,16 +1185,16 @@
       <c r="I14" t="str">
         <v>정교수</v>
       </c>
-      <c r="J14" t="str">
-        <v>3</v>
-      </c>
-      <c r="K14" t="str">
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
         <v>40</v>
       </c>
-      <c r="L14" t="str">
-        <v>2</v>
-      </c>
-      <c r="M14" t="str">
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
         <v>10</v>
       </c>
       <c r="N14" t="str">
@@ -1215,10 +1203,10 @@
       <c r="O14" t="str">
         <v>수</v>
       </c>
-      <c r="P14" t="str">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="str">
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
         <v>4</v>
       </c>
       <c r="R14" t="str">
@@ -1256,16 +1244,16 @@
       <c r="I15" t="str">
         <v>김교수</v>
       </c>
-      <c r="J15" t="str">
-        <v>3</v>
-      </c>
-      <c r="K15" t="str">
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
         <v>50</v>
       </c>
-      <c r="L15" t="str">
+      <c r="L15">
         <v>1</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M15">
         <v>10</v>
       </c>
       <c r="N15" t="str">
@@ -1315,16 +1303,16 @@
       <c r="I16" t="str">
         <v>박강사</v>
       </c>
-      <c r="J16" t="str">
-        <v>2</v>
-      </c>
-      <c r="K16" t="str">
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <v>45</v>
       </c>
-      <c r="L16" t="str">
+      <c r="L16">
         <v>1</v>
       </c>
-      <c r="M16" t="str">
+      <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="str">
@@ -1333,10 +1321,10 @@
       <c r="O16" t="str">
         <v>금</v>
       </c>
-      <c r="P16" t="str">
+      <c r="P16">
         <v>1</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16" t="str">
@@ -1374,16 +1362,16 @@
       <c r="I17" t="str">
         <v>강교수</v>
       </c>
-      <c r="J17" t="str">
-        <v>3</v>
-      </c>
-      <c r="K17" t="str">
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
         <v>30</v>
       </c>
-      <c r="L17" t="str">
-        <v>2</v>
-      </c>
-      <c r="M17" t="str">
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
         <v>11</v>
       </c>
       <c r="N17" t="str">
@@ -1392,10 +1380,10 @@
       <c r="O17" t="str">
         <v>월</v>
       </c>
-      <c r="P17" t="str">
+      <c r="P17">
         <v>6</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="Q17">
         <v>7</v>
       </c>
       <c r="R17" t="str">
@@ -1433,16 +1421,16 @@
       <c r="I18" t="str">
         <v>이교수</v>
       </c>
-      <c r="J18" t="str">
-        <v>3</v>
-      </c>
-      <c r="K18" t="str">
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
         <v>30</v>
       </c>
-      <c r="L18" t="str">
-        <v>3</v>
-      </c>
-      <c r="M18" t="str">
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
         <v>11</v>
       </c>
       <c r="N18" t="str">
@@ -1451,10 +1439,10 @@
       <c r="O18" t="str">
         <v>수</v>
       </c>
-      <c r="P18" t="str">
+      <c r="P18">
         <v>6</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="Q18">
         <v>8</v>
       </c>
       <c r="R18" t="str">
@@ -1492,16 +1480,16 @@
       <c r="I19" t="str">
         <v>박교수</v>
       </c>
-      <c r="J19" t="str">
-        <v>3</v>
-      </c>
-      <c r="K19" t="str">
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
         <v>35</v>
       </c>
-      <c r="L19" t="str">
-        <v>3</v>
-      </c>
-      <c r="M19" t="str">
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
         <v>12</v>
       </c>
       <c r="N19" t="str">
@@ -1551,16 +1539,16 @@
       <c r="I20" t="str">
         <v>이교수</v>
       </c>
-      <c r="J20" t="str">
-        <v>2</v>
-      </c>
-      <c r="K20" t="str">
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
         <v>40</v>
       </c>
-      <c r="L20" t="str">
+      <c r="L20">
         <v>1</v>
       </c>
-      <c r="M20" t="str">
+      <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="str">
@@ -1569,10 +1557,10 @@
       <c r="O20" t="str">
         <v>월</v>
       </c>
-      <c r="P20" t="str">
+      <c r="P20">
         <v>1</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20" t="str">
@@ -1583,6 +1571,8 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S19"/>
+  <pageMargins left="0.6997222304344177" right="0.6997222304344177" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:S20"/>
   </ignoredErrors>
